--- a/dados/Base_de_indisponibilidade.xlsx
+++ b/dados/Base_de_indisponibilidade.xlsx
@@ -8,24 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://campsegvig.sharepoint.com/sites/CSC-Implantacao/Documentos Compartilhados/Operações - Área 03/BANCO DE DADOS/DASHBOARD DIRETORIA/autodefesa-painel/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{3E15FE9D-4A06-4C4D-B9CF-996B0A247E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="14_{3E15FE9D-4A06-4C4D-B9CF-996B0A247E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{119B9309-77E8-4984-967B-BFA4067963FD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="50">
   <si>
     <t>Código da conta</t>
   </si>
@@ -166,6 +180,15 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Unidade passou por mudança de endereço</t>
+  </si>
+  <si>
+    <t>Atendimento técnico realizado em campo</t>
+  </si>
+  <si>
+    <t>7422 - CREFISA - 4113 PATOS DE MINAS MG (CREFISA)</t>
   </si>
 </sst>
 </file>
@@ -489,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -501,7 +524,7 @@
     <col min="7" max="7" width="11.109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="40.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="43" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -558,6 +581,15 @@
       <c r="G2" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="H2" s="1">
+        <v>46204</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -581,6 +613,15 @@
       <c r="G3" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="H3" s="1">
+        <v>46204</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -604,6 +645,15 @@
       <c r="G4" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="H4" s="1">
+        <v>46204</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -627,6 +677,15 @@
       <c r="G5" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="H5" s="1">
+        <v>46204</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -650,6 +709,15 @@
       <c r="G6" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="H6" s="1">
+        <v>46205</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -668,11 +736,20 @@
         <v>46203</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="H7" s="1">
+        <v>46205</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -691,11 +768,20 @@
         <v>46203</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="H8" s="1">
+        <v>46205</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -1287,32 +1373,36 @@
         <v>42</v>
       </c>
     </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="2">
+        <v>7422</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="1d5c0da2-bbfc-47d9-b6b5-e306f5be4e89" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="59493c50-1a97-4baf-8393-5ecd9f8353af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009FF7DDFF717A644381C29F2B9C89CFB4" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="c58ff28f6439cefa5d9fc2d1f4456076">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="59493c50-1a97-4baf-8393-5ecd9f8353af" xmlns:ns3="1d5c0da2-bbfc-47d9-b6b5-e306f5be4e89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ee2a39c2b9e3016efd0900d8c88cf66" ns2:_="" ns3:_="">
     <xsd:import namespace="59493c50-1a97-4baf-8393-5ecd9f8353af"/>
@@ -1513,26 +1603,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{586E2403-551D-430D-B750-5E84E6E3FAA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d5c0da2-bbfc-47d9-b6b5-e306f5be4e89"/>
-    <ds:schemaRef ds:uri="59493c50-1a97-4baf-8393-5ecd9f8353af"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="1d5c0da2-bbfc-47d9-b6b5-e306f5be4e89" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="59493c50-1a97-4baf-8393-5ecd9f8353af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767C8547-3253-4C11-B5FD-48799F78BA55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D3035FF-A530-4B03-9245-B52EFC1B2BB3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1549,4 +1640,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{586E2403-551D-430D-B750-5E84E6E3FAA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d5c0da2-bbfc-47d9-b6b5-e306f5be4e89"/>
+    <ds:schemaRef ds:uri="59493c50-1a97-4baf-8393-5ecd9f8353af"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767C8547-3253-4C11-B5FD-48799F78BA55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>